--- a/impresoras_al_dia.xlsx
+++ b/impresoras_al_dia.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,17 +57,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0092D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF6666"/>
+        <fgColor rgb="0092D050"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,9 +101,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -486,6 +478,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,6 +517,11 @@
           <t>IMPRESIONES_TOTALES</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>NUMERO_SERIE</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -549,6 +547,7 @@
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -574,6 +573,7 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -599,6 +599,7 @@
       <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -627,10 +628,15 @@
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>115946</v>
+        <v>116886</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Z5THBAGBC00113N</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -659,11 +665,16 @@
           <t>192.168.0.101</t>
         </is>
       </c>
-      <c r="F6" s="7" t="n">
-        <v>53</v>
+      <c r="F6" s="6" t="n">
+        <v>50</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>154793</v>
+        <v>155192</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Z5THBAGBC00009K</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -693,44 +704,42 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>148898</v>
+        <v>153140</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Z5THBAGBC00050W</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>00:15:99:97:37:A6</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>ML3710</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>CONTROL2</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>192.168.1.47</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>325889</v>
-      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -758,11 +767,16 @@
           <t>192.168.0.28</t>
         </is>
       </c>
-      <c r="F9" s="8" t="n">
-        <v>10</v>
+      <c r="F9" s="7" t="n">
+        <v>76</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>184817</v>
+        <v>185854</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Z5THB8GC6F003HR</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -789,6 +803,7 @@
       <c r="E10" s="3" t="inlineStr"/>
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -816,45 +831,43 @@
           <t>192.168.0.80</t>
         </is>
       </c>
-      <c r="F11" s="7" t="n">
-        <v>54</v>
+      <c r="F11" s="6" t="n">
+        <v>43</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>112289</v>
+        <v>113186</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Z5THB8GC6F001EM</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>00:15:99:97:37:AF</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>ML3710</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>CONTADURIA</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>192.168.0.32</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>77</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>159642</v>
-      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -882,11 +895,16 @@
           <t>192.168.0.81</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n">
-        <v>23</v>
+      <c r="F13" s="7" t="n">
+        <v>73</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>200468</v>
+        <v>202568</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Z5THBAGBC00004W</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -913,9 +931,10 @@
       <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/impresoras_al_dia.xlsx
+++ b/impresoras_al_dia.xlsx
@@ -52,7 +52,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="0092D050"/>
       </patternFill>
     </fill>
     <fill>
@@ -62,7 +62,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0092D050"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,17 +89,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -544,10 +544,22 @@
           <t>INGENIERIA</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>192.168.0.59</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>12400</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>CNHXJ23710</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -570,10 +582,22 @@
           <t>GARANTIA</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>192.168.0.30</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>49188</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>BRBFCCKX0K</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -596,120 +620,132 @@
           <t>DESARROLLO1</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>192.168.0.71</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>12677</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>BRBSHCQ3PB</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>00:15:99:97:38:3E</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>ML3710</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>DESARROLLO2</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>192.168.0.70</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>116886</v>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>117141</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Z5THBAGBC00113N</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>00:15:99:97:3B:83</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>ML3710</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>MATERIAS PRIMAS</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>192.168.0.101</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>155192</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>155303</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Z5THBAGBC00009K</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>00:15:99:97:37:AA</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>ML3710</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>CONTROL1</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>192.168.1.46</t>
         </is>
       </c>
-      <c r="F7" s="7" t="n">
-        <v>88</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>153140</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>154586</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Z5THBAGBC00050W</t>
         </is>
@@ -736,108 +772,120 @@
           <t>CONTROL2</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>192.168.1.47</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>328508</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Z5THBAGBC00125X</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>00:15:99:A8:A3:FE</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>ML3710</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>NO BETA</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>192.168.0.28</t>
         </is>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>76</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>185854</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>186089</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Z5THB8GC6F003HR</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>00:15:99:97:38:3D</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>SAMSUNG</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>ML3710</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>SUPERVISORES</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>00:15:99:A8:A3:C3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>ML3710</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>192.168.0.80</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>113186</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="F11" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>113551</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Z5THB8GC6F001EM</t>
         </is>
@@ -846,7 +894,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>00:15:99:97:37:AF</t>
+          <t>00:15:99:8D:02:A1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -864,44 +912,56 @@
           <t>CONTADURIA</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>192.168.0.32</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>34259</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Z5THBADB800079R</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>00:15:99:97:3B:85</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>SAMSUNG</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>ML3710</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>BETA</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>192.168.0.81</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>202568</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="F13" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>203097</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Z5THBAGBC00004W</t>
         </is>
@@ -928,10 +988,22 @@
           <t>AR</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>192.168.0.35</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>84434</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>5178ZB30564</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H14"/>

--- a/impresoras_al_dia.xlsx
+++ b/impresoras_al_dia.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$H$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -52,7 +52,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0092D050"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -62,7 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="0092D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF6666"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +89,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -468,12 +476,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -544,22 +552,10 @@
           <t>INGENIERIA</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>192.168.0.59</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>12400</v>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>CNHXJ23710</t>
-        </is>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -582,431 +578,483 @@
           <t>GARANTIA</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>192.168.0.30</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>49188</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>BRBFCCKX0K</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>48:0F:CF:F9:41:7B</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>00:15:99:A8:A3:E9</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Samsung ML-371x Series</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>DESARROLLO1</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>192.168.0.71</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>144042</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Z5THB8GC6F003RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>00:15:99:97:38:3E</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Samsung ML-371x Series</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>DESARROLLO2</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>192.168.0.70</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>117792</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Z5THBAGBC00113N</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>00:15:99:97:3B:83</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Samsung ML-371x Series</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>MATERIAS PRIMAS</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>192.168.0.101</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>155916</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Z5THBAGBC00009K</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>00:15:99:97:37:AA</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Samsung ML-371x Series</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>CONTROL1</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>192.168.1.46</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>160519</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Z5THBAGBC00050W</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>00:15:99:97:37:A6</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Samsung ML-371x Series</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>CONTROL2</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>192.168.1.47</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>331923</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Z5THBAGBC00125X</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>00:15:99:A8:A3:FE</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Samsung ML-371x Series</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>NO BETA</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>192.168.0.28</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>187627</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Z5THB8GC6F003HR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>00:15:99:97:38:3D</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SAMSUNG</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ML3710</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>SUPERVISORES</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>00:15:99:A8:A3:C3</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Samsung ML-371x Series</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>192.168.0.80</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>114009</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Z5THB8GC6F001EM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>00:15:99:8D:02:A1</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Samsung ML-371x Series</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>CONTADURIA</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>192.168.0.32</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>36793</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Z5THBADB800079R</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>00:15:99:97:3B:85</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Samsung ML-371x Series</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>BETA</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>192.168.0.81</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>206138</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Z5THBAGBC00004W</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>58:38:79:19:20:EA</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Ricoh</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>RICOH SP 3710SF V1.03 / RICOH Network Printer C model / RICOH Network Scanner C model / RICOH Network Facsimile C model</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>192.168.0.35</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>85453</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>5178ZB30564</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>00:21:5A:FE:24:37</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>LASERJET M402dn</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>DESARROLLO1</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>192.168.0.71</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>12677</v>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>BRBSHCQ3PB</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>00:15:99:97:38:3E</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>ML3710</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>DESARROLLO2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>192.168.0.70</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>117141</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Z5THBAGBC00113N</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>00:15:99:97:3B:83</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>ML3710</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>MATERIAS PRIMAS</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>192.168.0.101</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>155303</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Z5THBAGBC00009K</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>00:15:99:97:37:AA</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ML3710</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>192.168.1.46</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>154586</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Z5THBAGBC00050W</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>00:15:99:97:37:A6</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>ML3710</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL2</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>192.168.1.47</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>328508</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Z5THBAGBC00125X</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>00:15:99:A8:A3:FE</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>ML3710</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>NO BETA</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>192.168.0.28</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>186089</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Z5THB8GC6F003HR</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>00:15:99:97:38:3D</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>SAMSUNG</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>ML3710</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>SUPERVISORES</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>00:15:99:A8:A3:C3</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>ML3710</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>192.168.0.80</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>113551</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Z5THB8GC6F001EM</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>00:15:99:8D:02:A1</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>ML3710</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>CONTADURIA</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>192.168.0.32</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>34259</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Z5THBADB800079R</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>00:15:99:97:3B:85</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SAMSUNG</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>ML3710</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>BETA</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>192.168.0.81</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>203097</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Z5THBAGBC00004W</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>58:38:79:19:20:EA</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>RICOH</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>SP 3710SF</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>192.168.0.35</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>84434</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>5178ZB30564</t>
-        </is>
-      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Laserjet 2430</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>PLANEAMIENTO</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>192.168.0.68</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>00:0F:20:C6:4B:09</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Laserjet 2430</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>SISTEMAS</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>192.168.1.215</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>